--- a/data/Список оборудования.xlsx
+++ b/data/Список оборудования.xlsx
@@ -548,12 +548,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>27.12.2015</t>
+          <t>27.12.2025</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>27.12.2015</t>
+          <t>27.12.2025</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -601,12 +601,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>15.08.2013</t>
+          <t>15.08.2025</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15.08.2013</t>
+          <t>15.08.2025</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>07.01.2012</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>07.01.2012</t>
+          <t>07.01.2025</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12.07.2012</t>
+          <t>12.07.2025</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>12.07.2012</t>
+          <t>12.07.2025</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>26.08.2017</t>
+          <t>26.08.2025</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>26.08.2017</t>
+          <t>26.08.2025</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02.11.2023</t>
+          <t>02.11.2025</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>02.11.2023</t>
+          <t>02.11.2025</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03.09.2018</t>
+          <t>03.09.2025</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>03.09.2018</t>
+          <t>03.09.2025</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.03.2015</t>
+          <t>10.03.2025</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>10.03.2015</t>
+          <t>10.03.2025</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>08.03.2010</t>
+          <t>08.03.2025</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>08.03.2010</t>
+          <t>08.03.2025</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1025,12 +1025,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>16.04.2021</t>
+          <t>16.04.2025</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16.04.2021</t>
+          <t>16.04.2025</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03.05.2018</t>
+          <t>03.05.2025</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>03.05.2018</t>
+          <t>03.05.2025</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>21.06.2016</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>21.06.2016</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>11.04.2019</t>
+          <t>11.04.2025</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>11.04.2019</t>
+          <t>11.04.2025</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19.10.2012</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>19.10.2012</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>17.02.2014</t>
+          <t>17.02.2025</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>17.02.2014</t>
+          <t>17.02.2025</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>22.09.2014</t>
+          <t>22.09.2025</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>22.09.2014</t>
+          <t>22.09.2025</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>01.06.2008</t>
+          <t>01.06.2025</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>01.06.2008</t>
+          <t>01.06.2025</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>18.09.2019</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>18.09.2019</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>11.06.2009</t>
+          <t>11.06.2025</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>11.06.2009</t>
+          <t>11.06.2025</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>07.05.2013</t>
+          <t>07.05.2025</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>07.05.2013</t>
+          <t>07.05.2025</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>05.07.2022</t>
+          <t>05.07.2025</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>05.07.2022</t>
+          <t>05.07.2025</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>24.11.2018</t>
+          <t>24.11.2025</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>24.11.2018</t>
+          <t>24.11.2025</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>25.11.2016</t>
+          <t>25.11.2025</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>25.11.2016</t>
+          <t>25.11.2025</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09.01.2010</t>
+          <t>09.01.2025</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>09.01.2010</t>
+          <t>09.01.2025</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>27.03.2011</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>27.03.2011</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>27.05.2016</t>
+          <t>27.05.2025</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>27.05.2016</t>
+          <t>27.05.2025</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>29.11.2014</t>
+          <t>29.11.2025</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>24.05.2020</t>
+          <t>24.05.2025</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>24.05.2020</t>
+          <t>24.05.2025</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17.09.2016</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>17.09.2016</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>05.08.2011</t>
+          <t>05.08.2025</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>05.08.2011</t>
+          <t>05.08.2025</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>26.07.2018</t>
+          <t>26.07.2025</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>26.07.2018</t>
+          <t>26.07.2025</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>09.06.2017</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>09.06.2017</t>
+          <t>09.06.2025</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>26.01.2008</t>
+          <t>26.01.2025</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>26.01.2008</t>
+          <t>26.01.2025</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>01.03.2015</t>
+          <t>01.03.2025</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>01.03.2015</t>
+          <t>01.03.2025</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>22.11.2009</t>
+          <t>22.11.2025</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>22.11.2009</t>
+          <t>22.11.2025</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>29.12.2009</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>29.12.2009</t>
+          <t>29.12.2025</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>30.12.2009</t>
+          <t>30.12.2025</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>30.12.2009</t>
+          <t>30.12.2025</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>12.01.2013</t>
+          <t>12.01.2025</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>12.01.2013</t>
+          <t>12.01.2025</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>19.08.2012</t>
+          <t>19.08.2025</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>19.08.2012</t>
+          <t>19.08.2025</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>05.07.2014</t>
+          <t>05.07.2025</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>05.07.2014</t>
+          <t>05.07.2025</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>25.03.2008</t>
+          <t>25.03.2025</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>25.03.2008</t>
+          <t>25.03.2025</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>21.08.2009</t>
+          <t>21.08.2025</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>21.08.2009</t>
+          <t>21.08.2025</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>08.09.2013</t>
+          <t>08.09.2025</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>08.09.2013</t>
+          <t>08.09.2025</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>23.10.2011</t>
+          <t>23.10.2025</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>23.10.2011</t>
+          <t>23.10.2025</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>15.08.2010</t>
+          <t>15.08.2025</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>15.08.2010</t>
+          <t>15.08.2025</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>30.09.2021</t>
+          <t>30.09.2025</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>30.09.2021</t>
+          <t>30.09.2025</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>27.03.2012</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>27.03.2012</t>
+          <t>27.03.2025</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>30.11.2008</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>30.11.2008</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>05.02.2010</t>
+          <t>05.02.2025</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>05.02.2010</t>
+          <t>05.02.2025</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>19.10.2019</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>19.10.2019</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>13.04.2023</t>
+          <t>13.04.2025</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>13.04.2023</t>
+          <t>13.04.2025</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>15.11.2023</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>15.11.2023</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>06.10.2020</t>
+          <t>06.10.2025</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>06.10.2020</t>
+          <t>06.10.2025</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>11.12.2016</t>
+          <t>11.12.2025</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>11.12.2016</t>
+          <t>11.12.2025</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>09.01.2017</t>
+          <t>09.01.2025</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>09.01.2017</t>
+          <t>09.01.2025</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>20.01.2016</t>
+          <t>20.01.2025</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>20.01.2016</t>
+          <t>20.01.2025</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>23.06.2017</t>
+          <t>23.06.2025</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>23.06.2017</t>
+          <t>23.06.2025</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>11.07.2022</t>
+          <t>11.07.2025</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>11.07.2022</t>
+          <t>11.07.2025</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>17.09.2018</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>17.09.2018</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>10.05.2020</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>10.05.2020</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>18.09.2013</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>18.09.2013</t>
+          <t>18.09.2025</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>13.11.2009</t>
+          <t>13.11.2025</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>13.11.2009</t>
+          <t>13.11.2025</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>13.03.2012</t>
+          <t>13.03.2025</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>13.03.2012</t>
+          <t>13.03.2025</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>09.11.2016</t>
+          <t>09.11.2025</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>09.11.2016</t>
+          <t>09.11.2025</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>14.11.2021</t>
+          <t>14.11.2025</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>14.11.2021</t>
+          <t>14.11.2025</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>12.04.2012</t>
+          <t>12.04.2025</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>12.04.2012</t>
+          <t>12.04.2025</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>09.10.2017</t>
+          <t>09.10.2025</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>09.10.2017</t>
+          <t>09.10.2025</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>04.10.2023</t>
+          <t>04.10.2025</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>04.10.2023</t>
+          <t>04.10.2025</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>21.02.2009</t>
+          <t>21.02.2025</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>21.02.2009</t>
+          <t>21.02.2025</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>07.12.2018</t>
+          <t>07.12.2025</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>07.12.2018</t>
+          <t>07.12.2025</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>04.12.2020</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>04.12.2020</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>24.08.2023</t>
+          <t>24.08.2025</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>24.08.2023</t>
+          <t>24.08.2025</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>03.07.2021</t>
+          <t>03.07.2025</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>03.07.2021</t>
+          <t>03.07.2025</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>20.08.2011</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>20.08.2011</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>06.04.2010</t>
+          <t>06.04.2025</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>06.04.2010</t>
+          <t>06.04.2025</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>03.01.2016</t>
+          <t>03.01.2025</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>03.01.2016</t>
+          <t>03.01.2025</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>15.09.2010</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>15.09.2010</t>
+          <t>15.09.2025</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>24.06.2023</t>
+          <t>24.06.2025</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>24.06.2023</t>
+          <t>24.06.2025</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>18.05.2019</t>
+          <t>18.05.2025</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>18.05.2019</t>
+          <t>18.05.2025</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>17.06.2011</t>
+          <t>17.06.2025</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>17.06.2011</t>
+          <t>17.06.2025</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>28.08.2015</t>
+          <t>28.08.2025</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>28.08.2015</t>
+          <t>28.08.2025</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>17.11.2025</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>17.11.2025</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>04.12.2017</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>04.12.2017</t>
+          <t>04.12.2025</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>25.09.2017</t>
+          <t>25.09.2025</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>25.09.2017</t>
+          <t>25.09.2025</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>06.01.2017</t>
+          <t>06.01.2025</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>06.01.2017</t>
+          <t>06.01.2025</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>03.01.2018</t>
+          <t>03.01.2025</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>03.01.2018</t>
+          <t>03.01.2025</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>06.10.2014</t>
+          <t>06.10.2025</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>06.10.2014</t>
+          <t>06.10.2025</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>30.01.2010</t>
+          <t>30.01.2025</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>30.01.2010</t>
+          <t>30.01.2025</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>25.10.2025</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>25.10.2025</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>26.01.2009</t>
+          <t>26.01.2025</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>26.01.2009</t>
+          <t>26.01.2025</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>17.09.2014</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>17.09.2014</t>
+          <t>17.09.2025</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>09.05.2015</t>
+          <t>09.05.2025</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>09.05.2015</t>
+          <t>09.05.2025</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>24.05.2009</t>
+          <t>24.05.2025</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>24.05.2009</t>
+          <t>24.05.2025</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>08.11.2016</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>08.11.2016</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>07.11.2010</t>
+          <t>07.11.2025</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>07.11.2010</t>
+          <t>07.11.2025</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>24.09.2008</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>24.09.2008</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>27.10.2020</t>
+          <t>27.10.2025</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>27.10.2020</t>
+          <t>27.10.2025</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>16.03.2011</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>16.03.2011</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>29.09.2010</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>29.09.2010</t>
+          <t>29.09.2025</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>29.08.2018</t>
+          <t>29.08.2025</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>29.08.2018</t>
+          <t>29.08.2025</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
